--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0109.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0109.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Hoàn thành SkyArk Space Station để mở khóa</t>
+          <t>Hoàn thành Trạm Không Gian SkyArk để mở khóa</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Không có cấu hình phụ kiện</t>
+          <t>Chưa cấu hình phụ kiện</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Phụ kiện bị khóa</t>
+          <t>Trang sức đã bị khóa</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Phụ kiện đã được trang bị</t>
+          <t>Trang sức đã được trang bị</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Phụ kiện này không thể trang bị với trang phục đã chọn</t>
+          <t>Trang sức này không thể trang bị với bộ đồ đã chọn</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Chưa trang bị phụ kiện</t>
+          <t>Chưa trang bị Trang sức</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Tham số không hợp lệ</t>
+          <t>Thông số sai.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Tham số không hợp lệ</t>
+          <t>Thông số sai.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Nhiệm vụ hoàn thành</t>
+          <t>Hoàn thành nhiệm vụ</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Quests</t>
+          <t>Nhiệm vụ</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Nhiệm vụ hàng ngày</t>
+          <t>Nhiệm Vụ Hằng Ngày</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Tacet Field (First-Clear)</t>
+          <t>Tổ Tacet (Lần Đầu Vượt Ải)</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Medium Tacet Field: Transmitter</t>
+          <t>Tổ Tacet Cỡ Trung: Bộ Truyền Tín</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Medium Tacet Field: Weapon</t>
+          <t>Tổ Tacet Cỡ Trung: Vũ Khí</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Medium Tacet Field: Echo</t>
+          <t>Tổ Tacet Cỡ Trung: Echo</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Medium Tacet Field: Tacetite</t>
+          <t>Tổ Tacet Cỡ Trung: Tacetit</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Tempest Mephis - Early Access</t>
+          <t>Mephis Bão Tố - Truy Cập Sớm</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Feilian Beringal - Early Access</t>
+          <t>Feilian Beringal - Truy cập sớm</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Mech Abomination - Early Access</t>
+          <t>Quái Vật Cơ Khí - Truy Cập Sớm</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Cetus the Tidebreaker</t>
+          <t>Cetus Kẻ Phá Thủy Triều</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Scar - Early Access</t>
+          <t>Vết Sẹo - Truy Cập Sớm</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Sự kiện</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Lioness of Glory</t>
+          <t>Sư Tử Vinh Quang - Giai Đoạn Truy Cập Sớm</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Lioness of Glory - Early Access</t>
+          <t>Sư Tử Vinh Quang - Arsinosa</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Fenrico: Deliverance in the Deep</t>
+          <t>Fenrico: Sự Giải Thoát Trong Sâu Thẳm</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Fenrico: Deliverance in the Deep - Early Access</t>
+          <t>Fenrico: Giải Thoát Trong Vực Sâu - Early Access</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>The False Sovereign</t>
+          <t>Kẻ Quân Vương Giả Mạo</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Lady of the Sea</t>
+          <t>Nữ Thần Biển Cả</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>The False Sovereign - Early Access</t>
+          <t>Kẻ Quân Vương Giả Mạo - Truy Cập Sớm</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Lady of the Sea - Early Access</t>
+          <t>Nữ Thần Biển Cả - Early Access</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Hyvatia - Early Access</t>
+          <t>Hyvatia - Truy Cập Sớm</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Reactor Husk</t>
+          <t>Vỏ Lò Phản Ứng</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Reactor Husk - Early Access</t>
+          <t>Vỏ Lò Phản Ứng - Truy Cập Sớm</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Fallacy of Không Return</t>
+          <t>Ảo Tưởng Vô Hồi</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Weekly Challenges</t>
+          <t>Thử Thách Hàng Tuần</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Resonator Nursing Unit</t>
+          <t>Đơn Vị Điều Dưỡng Resonator</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Clamorling TDs in Lahai-Roi</t>
+          <t>Tổ Tacet Ồn Ào ở Lahai-Roi</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Roya Outcasts</t>
+          <t>Những Kẻ Bị Đày Đọa Roya</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Podcast Pioneer</t>
+          <t>Podcast Tiên Phong</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>"Dreaming Deep" Event</t>
+          <t>"Sự Kiện \"Giấc Mơ Sâu Thẳm\""</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>"Cubie Derby: Warmup" Event</t>
+          <t>"Sự kiện: Khởi Động Cuộc Đua Cubie"</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Thử thách Giả mạo: Rừng Sương mù</t>
+          <t>Thử Thách Giả Tạo: Rừng Sương Mù</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Thử thách Giả mạo: Khu rừng Ánh trăng</t>
+          <t>Thử Thách Giả Tạo: Rặng Cây Ánh Trăng</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Thử thách Giả mạo: Rừng Cúc vạn thọ</t>
+          <t>Thử Thách Giả Tạo: Rừng Cúc Vạn Thọ</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Thử thách Giả mạo: Tàn tích Cháy đỏ</t>
+          <t>Thử Thách Giả Tạo: Dấu Vết Lửa Đỏ</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Thử thách Giả mạo: Tàn tích Bị xói mòn</t>
+          <t>Thử Thách Giả Tạo: Tàn Phế Bị Xói Mòn</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Simulation Training</t>
+          <t>Huấn Luyện Mô Phỏng</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Thử thách Giả mạo</t>
+          <t>Thử Thách Giả Tạo</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>"Lament Recon: Solaris Soldier" Sự Kiện Giới Hạn</t>
+          <t>"Sự Tích Bi Hùng: Chiến Binh Solaris" Sự kiện giới hạn thời gian</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Phần Thưởng Tiến Độ Thám Hiểm Fabricatorium of the Deep</t>
+          <t>Phần Thưởng Khám Phá Fabricatorium Vực Sâu</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Phần Thưởng Tiến Độ Thám Hiểm Cao Nguyên Sanguis</t>
+          <t>Phần Thưởng Khám Phá Cao Nguyên Sanguis</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>"Operation: Frontier Renewal" Event</t>
+          <t>"Sự kiện \"Chiến dịch: Tái Sinh Biên Cương\""</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Moonlit Revelation</t>
+          <t>Bí Ẩn Dưới Trăng</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Thử Thách Rèn Luyện - Ragunna</t>
+          <t>Thử Thách Giả Tạo - Ragunna</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Masked Reverie</t>
+          <t>Mộng Ảo Đeo Mặt Nạ</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Rosemary's Apothecary</t>
+          <t>Hiệu Thuốc Của Rosemary</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Solis Tavern</t>
+          <t>Quán Rượu Solis</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Thử Thách Rèn Luyện: Bài Học Hoàng Hôn</t>
+          <t>Thử Thách Giả Tạo: Bài Học Hoàng Hôn</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Thử Thách Rèn Luyện: Bài Học Hư Không</t>
+          <t>Thử Thách Giả Tạo: Bài Học Hư Vô</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Thử Thách Rèn Luyện: Bài Học Than Hồng</t>
+          <t>Thử Thách Giả Tạo: Bài Học Tro Tàn</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Thử Thách Rèn Luyện: Tàn Tích Bị Lãng Quên</t>
+          <t>Thử Thách Giả Tạo: Dấu Vết Bị Lãng Quên</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Thử Thách Rèn Luyện: Tàn Tích Bị Ăn Mòn</t>
+          <t>Thử Thách Giả Tạo: Tàn Tích Bị Ăn Mòn</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Thử Thách Rèn Luyện: Vực Thẳm Khởi Đầu</t>
+          <t>Thử Thách Giả Tạo: Vực Khởi Đầu</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Thử Thách Rèn Luyện: Vực Thẳm Hy Sinh</t>
+          <t>Thử Thách Giả Tạo: Vực Hy Sinh</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Thử Thách Rèn Luyện: Vực Thẳm Thú Tội</t>
+          <t>Thử Thách Giả Tạo: Vực Thú Tội</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Thử Thách Rèn Luyện: Vườn Địa Đàng Cứu Rỗi</t>
+          <t>Thử Thách Giả Tạo: Vườn Cứu Rỗi</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Thử Thách Rèn Luyện: Vườn Địa Đàng Ngưỡng Mộ</t>
+          <t>Thử Thách Giả Tạo: Vườn Yêu Thương</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Gladiator's Portrait</t>
+          <t>Chân Dung Đấu Sĩ</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Exploring Solaris-3</t>
+          <t>Thám hiểm Solaris-3</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Ragunna Exploration</t>
+          <t>Thám Hiểm Ragunna</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Fagaceae Peninsula</t>
+          <t>Bán Đảo Fagaceae</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Kết Cục Của Kẻ Sám Hối</t>
+          <t>Kết Cục Của Kẻ Ăn Năn</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Adversity Exchange</t>
+          <t>Trao Đổi Nghịch Cảnh</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Simulation Training Cửa hàng</t>
+          <t>Kho Đồ Huấn Luyện Mô Phỏng</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Trial Cửa hàng</t>
+          <t>Kho Dữ Liệu Thử Nghiệm</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Overworld Collection</t>
+          <t>Bộ Sưu Tập Thế Giới Mở</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Animals</t>
+          <t>Động vật</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Câu Cá</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Insects</t>
+          <t>Bầy Côn Trùng</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Hẻm Núi Linh Hồn</t>
+          <t>Gorges of Spirits</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Đồng bằng Trung tâm</t>
+          <t>Central Plains</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Cao nguyên Desorock</t>
+          <t>Desorock Highland</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Thành Phố Cảng Guixu</t>
+          <t>Port City of Guixu</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Rừng Tối</t>
+          <t>Dim Forest</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Bãi Lầy Whining Aix</t>
+          <t>Whining Aix's Mire</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Luminous Shore</t>
+          <t>Bờ Biển Lấp Lánh</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15414,7 +15414,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Cooking</t>
+          <t>Nấu ăn</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -15484,7 +15484,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Synthesis</t>
+          <t>Tổng Hợp</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Triệu Tập</t>
+          <t>Triệu tập</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -15624,7 +15624,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Cửa hàng</t>
+          <t>Cửa Hàng</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -15694,7 +15694,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Waveplate Exchange</t>
+          <t>Trao Đổi Tấm Điều Chỉnh Sóng</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -15764,7 +15764,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Souvenir Cửa hàng</t>
+          <t>Cửa Hàng Lưu Niệm</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Giao Rương Sonance</t>
+          <t>Giao Hàng Quan Tài</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -15904,7 +15904,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Shifang Pharmacy</t>
+          <t>Dược Phẩm Shifang</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Ingredient Making</t>
+          <t>Chế biến Nguyên liệu</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Mahe's Grocery</t>
+          <t>Cửa Hàng Tạp Hóa Mahe</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Supply Pack</t>
+          <t>Gói Vật Tư</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16184,7 +16184,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Cửa Hàng KU-Money</t>
+          <t>Cửa hàng KU-Money</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Rosemary's Apothecary</t>
+          <t>Hiệu Thuốc Của Rosemary</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Trattoria Margherita</t>
+          <t>Quán Trattoria Margherita</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Kênh Nghệ Nhân</t>
+          <t>Kênh Nhà sưu tầm</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -16534,7 +16534,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Whisperins</t>
+          <t>Thì Thầm</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -16604,7 +16604,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Elite Class Whisperins</t>
+          <t>Whisperin Cấp Tinh Anh</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Elite Class Howlers</t>
+          <t>Hạng Tinh Anh - Loài Tru</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -16814,7 +16814,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Exiles</t>
+          <t>Những Kẻ Lưu Đày</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Overworld Exploration</t>
+          <t>Khám Phá Thế Giới Mở</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Clamorlings hoặc Tranquilites</t>
+          <t>Tacet Ồn Ào hay Tacet Yên Tĩnh</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17094,7 +17094,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Clamorlings hoặc Tranquilites Hạng Cao</t>
+          <t>Hạng Tinh Anh - Loài Gầm Thét hoặc Loài Yên Tĩnh</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Tacet Discords bị ảnh hưởng bởi Dark Tide</t>
+          <t>Tacet Discord bị ảnh hưởng bởi Dark Tide</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17234,7 +17234,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Hạng Cao bị ảnh hưởng bởi Dark Tide</t>
+          <t>Cấp Tinh Anh bị ảnh hưởng bởi Dark Tide</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Phần thưởng Trophy</t>
+          <t>Phần Thưởng Cúp</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -17374,7 +17374,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Phần thưởng Thân mật với Resonator</t>
+          <t>Phần Thưởng Thân Tình Resonator</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Phần thưởng Kho Dữ liệu</t>
+          <t>Phần Thưởng Kho Dữ Liệu</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Phần thưởng Sách Hướng dẫn</t>
+          <t>Phần Thưởng Sổ Hướng Dẫn</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Phần thưởng Thám hiểm</t>
+          <t>Phần Thưởng Thám Hiểm</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -17654,7 +17654,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Phần thưởng Đăng ký Trước Toàn cầu</t>
+          <t>Phần Thưởng Đăng Ký Trước Toàn Cầu</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -17724,7 +17724,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Phần thưởng Tham gia Sự kiện Sáng tạo Fan</t>
+          <t>Phần Thưởng Tham Gia Sự Kiện Sáng Tác Người Hâm Mộ</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Gói</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Tidal Exchange</t>
+          <t>Trao đổi Thủy Triều</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18074,7 +18074,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Companion Wish</t>
+          <t>Điều Ước Đồng Hành</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18144,7 +18144,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Điều Ước Lều Trại</t>
+          <t>Điều Ước Nhà Trọ</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Companions</t>
+          <t>Đồng Hành</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -18284,7 +18284,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Gian hàng Hội Chợ</t>
+          <t>Gian Hàng Hội Chợ</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -18494,7 +18494,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Yumyum Haven</t>
+          <t>Thiên Đường Ẩm Thực</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Xiang-LEE (Hoàn thành *Wish Upon the Moon IV* để mở khóa)</t>
+          <t>Hương-LY (Hoàn thành Ước Nguyện Trăng Rằm IV để mở khóa)</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -18634,7 +18634,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Collection Spots</t>
+          <t>Các Điểm Sưu Tập</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -18704,7 +18704,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Nhiệm vụ Chính "Đến Bờ Biển Cuối Cùng"</t>
+          <t>Nhiệm vụ chính "Tận cùng bờ cát"</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -18774,7 +18774,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Thử thách Chiến thuật của Yhoran</t>
+          <t>Thử Thách Chiến Thuật Yhoran</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Mê Cung Giấc Mộng</t>
+          <t>Mê Cung Somnium</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -18914,7 +18914,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Vực Sâu Ảo Cảnh: Tích Lũy Phantasm</t>
+          <t>Tổ Tacet Ảo Ảnh: Thu Thập Ảo Ảnh</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Hiện chưa khả dụng</t>
+          <t>Hiện không khả dụng</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19054,7 +19054,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Mua từ Cửa hàng</t>
+          <t>Mua từ Cửa Hàng</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Dances For Spring's Return</t>
+          <t>Điệu nhảy đón xuân về</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -19194,7 +19194,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Sự kiện</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -19264,7 +19264,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>"Cubie Derby: Warmup" Event</t>
+          <t>"Sự kiện: Khởi Động Cuộc Đua Cubie"</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -19334,7 +19334,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Synthesis - Purification</t>
+          <t>Tổng Hợp - Thanh Lọc</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -19404,7 +19404,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Synthesis - Conversion</t>
+          <t>Tổng Hợp - Chuyển Hóa</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -19474,7 +19474,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Synthesis - Constructing</t>
+          <t>Tổng Hợp - Chế Tạo</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Synthesis - Potion Making</t>
+          <t>Tổng Hợp - Chế Dược</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -19614,7 +19614,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Supply Pack</t>
+          <t>Gói Vật Tư</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -19684,7 +19684,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Phần thưởng thu thập Sonance Casket tại Rinascita</t>
+          <t>Phần thưởng cho Bộ Sưu Tập Sonance Casket tại Rinascita</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Phần thưởng Tiến độ Thám hiểm Ragunna</t>
+          <t>Phần thưởng cho Tiến Độ Thám Hiểm Ragunna</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
